--- a/java/verify/fixtures/空列词表（ods_t_name_kinds）.xlsx
+++ b/java/verify/fixtures/空列词表（ods_t_name_kinds）.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JR1"/>
+  <dimension ref="A1:KW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1805,6 +1805,161 @@
       <c r="JR1" t="inlineStr">
         <is>
           <t>出库数量</t>
+        </is>
+      </c>
+      <c r="JS1" t="inlineStr">
+        <is>
+          <t>心率</t>
+        </is>
+      </c>
+      <c r="JT1" t="inlineStr">
+        <is>
+          <t>脉搏</t>
+        </is>
+      </c>
+      <c r="JU1" t="inlineStr">
+        <is>
+          <t>剂次</t>
+        </is>
+      </c>
+      <c r="JV1" t="inlineStr">
+        <is>
+          <t>环数</t>
+        </is>
+      </c>
+      <c r="JW1" t="inlineStr">
+        <is>
+          <t>圈数</t>
+        </is>
+      </c>
+      <c r="JX1" t="inlineStr">
+        <is>
+          <t>血糖</t>
+        </is>
+      </c>
+      <c r="JY1" t="inlineStr">
+        <is>
+          <t>视力</t>
+        </is>
+      </c>
+      <c r="JZ1" t="inlineStr">
+        <is>
+          <t>剂量</t>
+        </is>
+      </c>
+      <c r="KA1" t="inlineStr">
+        <is>
+          <t>用药量</t>
+        </is>
+      </c>
+      <c r="KB1" t="inlineStr">
+        <is>
+          <t>收缩压</t>
+        </is>
+      </c>
+      <c r="KC1" t="inlineStr">
+        <is>
+          <t>舒张压</t>
+        </is>
+      </c>
+      <c r="KD1" t="inlineStr">
+        <is>
+          <t>血型</t>
+        </is>
+      </c>
+      <c r="KE1" t="inlineStr">
+        <is>
+          <t>过敏史</t>
+        </is>
+      </c>
+      <c r="KF1" t="inlineStr">
+        <is>
+          <t>体检结论</t>
+        </is>
+      </c>
+      <c r="KG1" t="inlineStr">
+        <is>
+          <t>课目</t>
+        </is>
+      </c>
+      <c r="KH1" t="inlineStr">
+        <is>
+          <t>驾驶员</t>
+        </is>
+      </c>
+      <c r="KI1" t="inlineStr">
+        <is>
+          <t>附件</t>
+        </is>
+      </c>
+      <c r="KJ1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="KK1" t="inlineStr">
+        <is>
+          <t>标记</t>
+        </is>
+      </c>
+      <c r="KL1" t="inlineStr">
+        <is>
+          <t>记录状态</t>
+        </is>
+      </c>
+      <c r="KM1" t="inlineStr">
+        <is>
+          <t>校验标记</t>
+        </is>
+      </c>
+      <c r="KN1" t="inlineStr">
+        <is>
+          <t>药品批号</t>
+        </is>
+      </c>
+      <c r="KO1" t="inlineStr">
+        <is>
+          <t>装备附件</t>
+        </is>
+      </c>
+      <c r="KP1" t="inlineStr">
+        <is>
+          <t>射击环数</t>
+        </is>
+      </c>
+      <c r="KQ1" t="inlineStr">
+        <is>
+          <t>接种剂次</t>
+        </is>
+      </c>
+      <c r="KR1" t="inlineStr">
+        <is>
+          <t>有效期</t>
+        </is>
+      </c>
+      <c r="KS1" t="inlineStr">
+        <is>
+          <t>到期日</t>
+        </is>
+      </c>
+      <c r="KT1" t="inlineStr">
+        <is>
+          <t>证件有效期</t>
+        </is>
+      </c>
+      <c r="KU1" t="inlineStr">
+        <is>
+          <t>整改期限</t>
+        </is>
+      </c>
+      <c r="KV1" t="inlineStr">
+        <is>
+          <t>完成时限</t>
+        </is>
+      </c>
+      <c r="KW1" t="inlineStr">
+        <is>
+          <t>保密期限</t>
         </is>
       </c>
     </row>
